--- a/zy70681/examples/巡检示例数据.xlsx
+++ b/zy70681/examples/巡检示例数据.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,21 @@
           <t>拍摄时间</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>巡检项编号</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>整改任务编号</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>复查编号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1490,6 +1505,13 @@
           <t>2024-01-15</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>I001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1522,6 +1544,17 @@
           <t>2024-01-15</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1554,6 +1587,17 @@
           <t>2024-01-16</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I004</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1584,6 +1628,21 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>R001</t>
         </is>
       </c>
     </row>
